--- a/VNFramework/Assets/StreamingAssets/story/zh/Test.xlsx
+++ b/VNFramework/Assets/StreamingAssets/story/zh/Test.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12180"/>
+    <workbookView windowWidth="28800" windowHeight="11460"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1268,6 +1268,9 @@
       <c r="C5" t="s">
         <v>21</v>
       </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
       <c r="G5" t="s">
         <v>24</v>
       </c>
@@ -1405,6 +1408,9 @@
       </c>
       <c r="C9" t="s">
         <v>21</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
       </c>
       <c r="G9" t="s">
         <v>18</v>

--- a/VNFramework/Assets/StreamingAssets/story/zh/Test.xlsx
+++ b/VNFramework/Assets/StreamingAssets/story/zh/Test.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="32">
   <si>
     <t>Name</t>
   </si>
@@ -122,10 +122,8 @@
     <t>choice</t>
   </si>
   <si>
-    <t>Test2</t>
-  </si>
-  <si>
-    <t>Test3</t>
+    <t>Test2
+Test3</t>
   </si>
 </sst>
 </file>
@@ -739,8 +737,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1063,7 +1064,7 @@
   <dimension ref="A1:P24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="39.2857142857143" customWidth="1"/>
+    <col min="2" max="2" width="24.8571428571429" customWidth="1"/>
     <col min="6" max="6" width="6.14285714285714" customWidth="1"/>
     <col min="7" max="7" width="12.1428571428571" customWidth="1"/>
     <col min="8" max="8" width="8.57142857142857" customWidth="1"/>
@@ -1921,22 +1922,18 @@
         <v>240</v>
       </c>
     </row>
-    <row r="24" spans="1:16">
+    <row r="24" ht="30" spans="1:16">
       <c r="A24" t="s">
         <v>30</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D24" t="s">
-        <v>32</v>
-      </c>
-      <c r="E24" t="s">
-        <v>32</v>
-      </c>
+      <c r="D24"/>
+      <c r="E24"/>
       <c r="M24">
         <f t="shared" si="0"/>
         <v>3</v>
